--- a/one up/普物實驗/Lab10 梅德爾實驗/E24146107_王翊權_預報10_表格.xlsx
+++ b/one up/普物實驗/Lab10 梅德爾實驗/E24146107_王翊權_預報10_表格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one up\普物實驗\Lab10 梅德爾實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{213FEC35-BB87-46CD-AAE8-324F9C749976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73CE031-BDBD-49C0-A8E2-2218DF5D2973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="18648" windowHeight="11784" activeTab="1" xr2:uid="{1CE423FF-CDFB-4175-A94B-2D2FC1D7D35B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="13">
   <si>
     <t>弓形波數</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,6 +84,10 @@
   </si>
   <si>
     <t>平均頻率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -91,7 +95,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -107,6 +114,14 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -116,7 +131,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -139,13 +154,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -155,12 +210,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -492,15 +569,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1475392-9E02-4310-AEB2-CF525FDF9A87}">
-  <dimension ref="B2:L20"/>
+  <dimension ref="B2:M20"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,77 +611,129 @@
       <c r="L3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M3" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>4</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="1">
+      <c r="D4" s="1">
+        <f>C4*M$4</f>
+        <v>49000</v>
+      </c>
+      <c r="E4" s="1">
+        <v>149</v>
+      </c>
+      <c r="F4" s="9">
+        <f>E4/B4*2</f>
+        <v>74.5</v>
+      </c>
+      <c r="G4" s="1">
+        <f>1/F4*(D4/L$4)^(1/2)</f>
+        <v>60.151554330890718</v>
+      </c>
+      <c r="H4" s="3">
+        <f>AVERAGE(G4:G7)</f>
+        <v>61.350534585536103</v>
+      </c>
+      <c r="I4" s="3">
         <v>60</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="J4" s="6">
+        <f>ABS((I4-H4)/I4)</f>
+        <v>2.2508909758935047E-2</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2.4399999999999999E-3</v>
+      </c>
+      <c r="M4" s="1">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
         <v>70</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="1">
-        <v>60</v>
-      </c>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D5" s="1">
+        <f t="shared" ref="D5:D7" si="0">C5*M$4</f>
+        <v>68600</v>
+      </c>
+      <c r="E5" s="1">
+        <v>129</v>
+      </c>
+      <c r="F5" s="9">
+        <f>E5/B5*2</f>
+        <v>86</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G7" si="1">1/F5*SQRT(D5/L$4)</f>
+        <v>61.655055558547808</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>170</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="1">
-        <v>60</v>
-      </c>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>166600</v>
+      </c>
+      <c r="E6" s="1">
+        <v>133.5</v>
+      </c>
+      <c r="F6" s="9">
+        <f>E6/B6*2</f>
+        <v>133.5</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="1"/>
+        <v>61.89581982772166</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1">
         <v>600</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="1">
-        <v>60</v>
-      </c>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>588000</v>
+      </c>
+      <c r="E7" s="1">
+        <v>125.8</v>
+      </c>
+      <c r="F7" s="9">
+        <f>E7/B7*2</f>
+        <v>251.6</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="1"/>
+        <v>61.699708624984218</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -618,7 +750,7 @@
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>4</v>
       </c>
@@ -635,7 +767,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>2</v>
       </c>
@@ -652,7 +784,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>1</v>
       </c>
@@ -669,12 +801,12 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>0</v>
       </c>
@@ -713,16 +845,35 @@
       <c r="C17" s="1">
         <v>550</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1">
+      <c r="D17" s="1">
+        <f>C17*M$4</f>
+        <v>539000</v>
+      </c>
+      <c r="E17" s="1">
+        <v>135.80000000000001</v>
+      </c>
+      <c r="F17" s="9">
+        <f>E17/B17*2</f>
+        <v>135.80000000000001</v>
+      </c>
+      <c r="G17" s="1">
+        <f>1/F17*(D17/L$17)^(1/2)</f>
+        <v>61.810733177362664</v>
+      </c>
+      <c r="H17" s="3">
+        <f>AVERAGE(G17:G18)</f>
+        <v>62.044565073050009</v>
+      </c>
+      <c r="I17" s="3">
         <v>60</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="6">
+        <f>ABS((I17-H17)/I17)</f>
+        <v>3.4076084550833483E-2</v>
+      </c>
+      <c r="L17" s="1">
+        <v>7.6499999999999997E-3</v>
+      </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
@@ -731,15 +882,24 @@
       <c r="C18" s="1">
         <v>140</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1">
-        <v>60</v>
-      </c>
-      <c r="J18" s="1"/>
+      <c r="D18" s="1">
+        <f>C18*M$4</f>
+        <v>137200</v>
+      </c>
+      <c r="E18" s="1">
+        <v>136</v>
+      </c>
+      <c r="F18" s="9">
+        <f>E18/B18*2</f>
+        <v>68</v>
+      </c>
+      <c r="G18" s="1">
+        <f>1/F18*(D18/L$17)^(1/2)</f>
+        <v>62.278396968737361</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
@@ -776,6 +936,14 @@
       <c r="J20" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="I17:I18"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -783,15 +951,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{762E4BB6-B4A1-4A26-8EA5-6843EA026EDD}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -822,60 +990,103 @@
       <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>3</v>
       </c>
       <c r="B3" s="1">
         <v>70</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1">
+      <c r="C3" s="1">
+        <f>B3*L$3</f>
+        <v>68600</v>
+      </c>
+      <c r="D3" s="9">
+        <v>149.30000000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <f>D3/A3*2</f>
+        <v>99.533333333333346</v>
+      </c>
+      <c r="F3" s="1">
+        <f>1/E3*(C3/K$3)^(1/2)</f>
+        <v>30.085885033075922</v>
+      </c>
+      <c r="G3" s="3">
+        <f>AVERAGE(F3:F5)</f>
+        <v>29.839477754102656</v>
+      </c>
+      <c r="H3" s="3">
         <v>30</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I3" s="6">
+        <f>ABS((G3-H3)/H3)</f>
+        <v>5.350741529911455E-3</v>
+      </c>
+      <c r="K3" s="1">
+        <v>7.6499999999999997E-3</v>
+      </c>
+      <c r="L3" s="1">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>160</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1">
-        <v>30</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C4" s="1">
+        <f>B4*L$3</f>
+        <v>156800</v>
+      </c>
+      <c r="D4" s="9">
+        <v>151.6</v>
+      </c>
+      <c r="E4" s="1">
+        <f>D4/A4*2</f>
+        <v>151.6</v>
+      </c>
+      <c r="F4" s="1">
+        <f>1/E4*(C4/K$3)^(1/2)</f>
+        <v>29.863665351879174</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1">
         <v>620</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1">
-        <v>30</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C5" s="1">
+        <f>B5*L$3</f>
+        <v>607600</v>
+      </c>
+      <c r="D5" s="9">
+        <v>150.69999999999999</v>
+      </c>
+      <c r="E5" s="1">
+        <f>D5/A5*2</f>
+        <v>301.39999999999998</v>
+      </c>
+      <c r="F5" s="1">
+        <f>1/E5*(C5/K$3)^(1/2)</f>
+        <v>29.568882877352873</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -892,7 +1103,7 @@
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -909,11 +1120,11 @@
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <v>710</v>
       </c>
       <c r="C8" s="1"/>
@@ -927,6 +1138,11 @@
       <c r="I8" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="H3:H5"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
